--- a/outputs/534-26.xlsx
+++ b/outputs/534-26.xlsx
@@ -142,15 +142,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -344,7 +344,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AA1"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.87890625" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10"/>
@@ -466,7 +466,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AA1"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.87890625" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10"/>

--- a/outputs/534-26.xlsx
+++ b/outputs/534-26.xlsx
@@ -343,7 +343,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AA1"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr defaultColWidth="8.87890625" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7.67"/>
@@ -390,63 +390,6 @@
       </c>
       <c r="H1" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="I1" s="3" t="n">
-        <v>44166</v>
-      </c>
-      <c r="J1" s="3" t="n">
-        <v>44197</v>
-      </c>
-      <c r="K1" s="3" t="n">
-        <v>44228</v>
-      </c>
-      <c r="L1" s="3" t="n">
-        <v>44256</v>
-      </c>
-      <c r="M1" s="3" t="n">
-        <v>44287</v>
-      </c>
-      <c r="N1" s="3" t="n">
-        <v>44317</v>
-      </c>
-      <c r="O1" s="3" t="n">
-        <v>44348</v>
-      </c>
-      <c r="P1" s="3" t="n">
-        <v>44378</v>
-      </c>
-      <c r="Q1" s="3" t="n">
-        <v>44409</v>
-      </c>
-      <c r="R1" s="3" t="n">
-        <v>44440</v>
-      </c>
-      <c r="S1" s="3" t="n">
-        <v>44470</v>
-      </c>
-      <c r="T1" s="3" t="n">
-        <v>44501</v>
-      </c>
-      <c r="U1" s="3" t="n">
-        <v>44531</v>
-      </c>
-      <c r="V1" s="3" t="n">
-        <v>44562</v>
-      </c>
-      <c r="W1" s="3" t="n">
-        <v>44593</v>
-      </c>
-      <c r="X1" s="3" t="n">
-        <v>44621</v>
-      </c>
-      <c r="Y1" s="3" t="n">
-        <v>44652</v>
-      </c>
-      <c r="Z1" s="3" t="n">
-        <v>44682</v>
-      </c>
-      <c r="AA1" s="3" t="n">
-        <v>44713</v>
       </c>
     </row>
   </sheetData>
